--- a/05_Figures/F06_prediction/proteins/T3/d_mcsa/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T3/d_mcsa/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -146,6 +146,9 @@
     <t xml:space="preserve">SLC25A12</t>
   </si>
   <si>
+    <t xml:space="preserve">TIMM21</t>
+  </si>
+  <si>
     <t xml:space="preserve">UCHL1</t>
   </si>
   <si>
@@ -158,279 +161,294 @@
     <t xml:space="preserve">CLIC4</t>
   </si>
   <si>
+    <t xml:space="preserve">SLC25A13</t>
+  </si>
+  <si>
     <t xml:space="preserve">SRSF2</t>
   </si>
   <si>
-    <t xml:space="preserve">TIMM21</t>
-  </si>
-  <si>
     <t xml:space="preserve">TYMP</t>
   </si>
   <si>
+    <t xml:space="preserve">ACTR1A</t>
+  </si>
+  <si>
     <t xml:space="preserve">AKT2</t>
   </si>
   <si>
     <t xml:space="preserve">ALDH7A1</t>
   </si>
   <si>
+    <t xml:space="preserve">GSTP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFDN5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRDX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKCQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKCSH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NME2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL37A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLPP</t>
+  </si>
+  <si>
     <t xml:space="preserve">DNAJA3</t>
   </si>
   <si>
+    <t xml:space="preserve">EIF6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FKBP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAP1L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAOB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANK4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDIA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3CB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB11B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A13</t>
+  </si>
+  <si>
     <t xml:space="preserve">FITM1</t>
   </si>
   <si>
-    <t xml:space="preserve">GSTP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFDN5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKCQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKCSH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAP1L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NME2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FKBP4</t>
+    <t xml:space="preserve">FKBP1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OXSM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS6KA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMYD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIFM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACYBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDNF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GANAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARNL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB5C</t>
   </si>
   <si>
     <t xml:space="preserve">RASA4</t>
   </si>
   <si>
-    <t xml:space="preserve">CLTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAOB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OXSM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDIA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3CB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANK4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMYD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FKBP1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB11B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS6KA3</t>
+    <t xml:space="preserve">RPS13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGLUCY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPG2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NTPCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRDX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKAB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A6</t>
   </si>
   <si>
     <t xml:space="preserve">SYNPO</t>
   </si>
   <si>
-    <t xml:space="preserve">VCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACYBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GANAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB5C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL37A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIFM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDNF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2S1</t>
+    <t xml:space="preserve">UQCRB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADH1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL8B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATPAF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BZW2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPNS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCDC22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCT5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCT8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHODH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1A1</t>
   </si>
   <si>
     <t xml:space="preserve">EIF3M</t>
   </si>
   <si>
-    <t xml:space="preserve">GARNL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPG2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIPSNAP3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NTPCR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKAB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UQCRB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARL8B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATPAF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BZW2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPNS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCT5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLASP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSNK2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEPTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGLUCY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHODH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EHD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2A</t>
-  </si>
-  <si>
     <t xml:space="preserve">FAM136A</t>
   </si>
   <si>
+    <t xml:space="preserve">FERMT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLNB</t>
+  </si>
+  <si>
     <t xml:space="preserve">FUS</t>
   </si>
   <si>
     <t xml:space="preserve">GDI1</t>
   </si>
   <si>
-    <t xml:space="preserve">GPAT3</t>
-  </si>
-  <si>
     <t xml:space="preserve">GPX4</t>
   </si>
   <si>
@@ -446,19 +464,19 @@
     <t xml:space="preserve">HEBP2</t>
   </si>
   <si>
+    <t xml:space="preserve">HYOU1</t>
+  </si>
+  <si>
     <t xml:space="preserve">IFITM1</t>
   </si>
   <si>
     <t xml:space="preserve">IMMT</t>
   </si>
   <si>
-    <t xml:space="preserve">MAPKAPK2</t>
-  </si>
-  <si>
     <t xml:space="preserve">MAPRE1</t>
   </si>
   <si>
-    <t xml:space="preserve">MPDU1</t>
+    <t xml:space="preserve">MME</t>
   </si>
   <si>
     <t xml:space="preserve">MPO</t>
@@ -473,9 +491,6 @@
     <t xml:space="preserve">MTHFD1</t>
   </si>
   <si>
-    <t xml:space="preserve">MTM1</t>
-  </si>
-  <si>
     <t xml:space="preserve">MTX1</t>
   </si>
   <si>
@@ -485,6 +500,9 @@
     <t xml:space="preserve">NDUFV2</t>
   </si>
   <si>
+    <t xml:space="preserve">NNMT</t>
+  </si>
+  <si>
     <t xml:space="preserve">PCCB</t>
   </si>
   <si>
@@ -497,12 +515,12 @@
     <t xml:space="preserve">PEBP1</t>
   </si>
   <si>
+    <t xml:space="preserve">PGLS</t>
+  </si>
+  <si>
     <t xml:space="preserve">PLGRKT</t>
   </si>
   <si>
-    <t xml:space="preserve">PMM2</t>
-  </si>
-  <si>
     <t xml:space="preserve">PPIA</t>
   </si>
   <si>
@@ -512,10 +530,13 @@
     <t xml:space="preserve">PRMT1</t>
   </si>
   <si>
+    <t xml:space="preserve">PSMA2</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSMA3</t>
   </si>
   <si>
-    <t xml:space="preserve">PSMA4</t>
+    <t xml:space="preserve">PSMB6</t>
   </si>
   <si>
     <t xml:space="preserve">PSMD14</t>
@@ -524,6 +545,9 @@
     <t xml:space="preserve">PSME1</t>
   </si>
   <si>
+    <t xml:space="preserve">PTBP1</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAB1B</t>
   </si>
   <si>
@@ -539,24 +563,24 @@
     <t xml:space="preserve">RPL14</t>
   </si>
   <si>
+    <t xml:space="preserve">RPL23</t>
+  </si>
+  <si>
     <t xml:space="preserve">RPS27</t>
   </si>
   <si>
-    <t xml:space="preserve">S100A6</t>
-  </si>
-  <si>
     <t xml:space="preserve">SAMM50</t>
   </si>
   <si>
+    <t xml:space="preserve">SLC25A46</t>
+  </si>
+  <si>
     <t xml:space="preserve">SLC35A4</t>
   </si>
   <si>
     <t xml:space="preserve">SMTNL1</t>
   </si>
   <si>
-    <t xml:space="preserve">SPCS1</t>
-  </si>
-  <si>
     <t xml:space="preserve">SPG7</t>
   </si>
   <si>
@@ -570,9 +594,6 @@
   </si>
   <si>
     <t xml:space="preserve">TIMM50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIMM9</t>
   </si>
   <si>
     <t xml:space="preserve">TMEM167A</t>
@@ -983,16 +1004,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.713388885594863</v>
+        <v>-0.408335001277076</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05</v>
+        <v>0.271428571428571</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1016,29 +1037,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.713388885594863</v>
+        <v>-0.408335001277076</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.572139303482587</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.45771144278607</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.675232725284975</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.611941633914574</v>
-      </c>
+        <v>0.271428571428571</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1062,2206 +1075,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.609648056399244</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0370130257826444</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.519822729848212</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.432819274575865</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.192730519678915</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.156461397305974</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.854578750569236</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.415131046199774</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.613974464700419</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.495298669169782</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-1.01903191878287</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.0214856012888971</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.17005580366964</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.791554123686376</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.237455152397571</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.285780347619007</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.168923831887944</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.171552673529795</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.159445638894382</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.495111654550357</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1.63320077249863</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.426031416522074</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-1.03079706935413</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.49038616104726</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-1.67128898478151</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.00237593544135573</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.413556944245817</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.312136648006841</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-1.18526386356484</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.488167104121009</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-1.56536451206298</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.243294898110786</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.673916375627672</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.17098359745431</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.441671177051105</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-1.49827214911343</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.443532854047571</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.824446203541781</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-1.0861267879702</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.12923413698864</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.95893427010024</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.0586798503676451</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-1.69961017492391</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.315540784824374</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.109828937424912</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.706592931517092</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.374773114261861</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-1.00188088828994</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.344222922889978</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.491917737435602</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.363900428876313</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.317172730825863</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.558874777562596</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.335138094616426</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.257798944587323</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.845373387482977</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.175803581700183</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.398033556072048</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.849829989970274</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.0720774790429358</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-1.06849054177961</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-1.13339080886756</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-1.34441468398855</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-1.57013972675851</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.791742423841076</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.282633908625759</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-3.83562997380022</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-1.04777295444028</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-1.35228334347152</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.342708707830668</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.408228586793634</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.275416613112918</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.19817296396857</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.380352100291566</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.950594116445843</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.0942081743112565</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.346919760469935</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.391362026796772</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.527016977326632</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.210271708573601</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-1.11338731896429</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-2.22143576816159</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.455395747391761</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-1.02544377105106</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.574706643685917</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.0509407116171918</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>0.129710316138418</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-1.04722866916249</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.195939858989224</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.494259261838333</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.758486559517947</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.370916277542289</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.527552102159332</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.870295594453956</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.696211468515678</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.11943378995352</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.6010867888645</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.214977914403018</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.776796694868903</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-1.88196267580518</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-1.10793818269651</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.64238702775699</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-1.15688150914365</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-1.677963294439</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.339499431673347</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.556572325724473</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.598465586418888</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.870383971548942</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.577623032242401</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.326892346148371</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.72676444856402</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.375885444687959</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.0766976652337195</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.835341446072317</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.414480993429694</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.099751518473445</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.640046929399114</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.935871612142884</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>0.431795539507006</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.514876583857802</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.998286096742455</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.735954458178576</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.960580048235485</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-1.17694716371575</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.75823635001114</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-1.4348323576816</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-1.48051953253489</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.970933072569671</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.593054447912397</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-1.95988340011936</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-2.08686656199752</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.244712205008746</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.13875568995189</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.89228106642173</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.578512736849219</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.910695642021959</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.265414606381629</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>0.309569943331046</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.17291077755786</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.286075914747218</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.886610502370564</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.197881855959668</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.02619614730787</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.942176546932614</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-1.02400390825096</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.988212178922064</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.718027523128396</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.780977412403547</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.206481362482833</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.483845298026208</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.862000068223895</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.096937233571255</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-1.45356913925992</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.0257289192986951</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.605288651543344</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.967829909240701</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.00327256336191128</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>0.233421402779455</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.295214571863115</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>0.336627746943076</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.147262608604731</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.519429401997325</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.579942111775989</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-1.33731638904725</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.326456199323788</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.19146298639485</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.982455661338839</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-1.9767858530766</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-1.06823223540665</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-1.32877447094226</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.910748656331151</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-1.44293007527253</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.752591853827058</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.376451063328811</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.0951609053193312</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>0.309424635168888</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.961973056177964</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-1.2554627340155</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-1.01028591097349</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-1.46086909088492</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.461916929520723</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-2.43448418512191</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.486506086706638</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.584254745152458</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.641501982530816</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.32992314943286</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-2.04755124614519</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-1.14391528597126</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-1.06260874459176</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-1.28136288584825</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.960144655681086</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.223962520086935</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.108256551462562</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>0.0330626680050874</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.61558383589158</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>0.17237301921573</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.717848600760868</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-2.14963769960899</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-2.1834788549179</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.172307213612718</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3304,7 +1117,7 @@
         <v>1.706</v>
       </c>
       <c r="E2" t="n">
-        <v>2.44686158458483</v>
+        <v>2.17506307531569</v>
       </c>
     </row>
     <row r="3">
@@ -3321,7 +1134,7 @@
         <v>4.218</v>
       </c>
       <c r="E3" t="n">
-        <v>0.477360010729452</v>
+        <v>2.58977881045125</v>
       </c>
     </row>
     <row r="4">
@@ -3338,7 +1151,7 @@
         <v>1.578</v>
       </c>
       <c r="E4" t="n">
-        <v>1.37332005178657</v>
+        <v>1.41050701698666</v>
       </c>
     </row>
     <row r="5">
@@ -3355,7 +1168,7 @@
         <v>3.683</v>
       </c>
       <c r="E5" t="n">
-        <v>3.58364339457401</v>
+        <v>3.31960947792276</v>
       </c>
     </row>
     <row r="6">
@@ -3372,7 +1185,7 @@
         <v>2.983</v>
       </c>
       <c r="E6" t="n">
-        <v>6.11914355396545</v>
+        <v>6.1639846678903</v>
       </c>
     </row>
     <row r="7">
@@ -3389,7 +1202,7 @@
         <v>2.44</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.512915853670243</v>
+        <v>-0.512470030674707</v>
       </c>
     </row>
     <row r="8">
@@ -3406,7 +1219,7 @@
         <v>3.879</v>
       </c>
       <c r="E8" t="n">
-        <v>0.164431479201134</v>
+        <v>0.249854392445997</v>
       </c>
     </row>
     <row r="9">
@@ -3423,7 +1236,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E9" t="n">
-        <v>1.30046401795161</v>
+        <v>1.23252348158381</v>
       </c>
     </row>
     <row r="10">
@@ -3440,7 +1253,7 @@
         <v>-1.918</v>
       </c>
       <c r="E10" t="n">
-        <v>1.34849566788106</v>
+        <v>1.30827944010513</v>
       </c>
     </row>
     <row r="11">
@@ -3457,7 +1270,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.927492698421463</v>
+        <v>0.967564885813052</v>
       </c>
     </row>
     <row r="12">
@@ -3474,7 +1287,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>1.0883160317874</v>
+        <v>1.0721005199618</v>
       </c>
     </row>
     <row r="13">
@@ -3491,7 +1304,7 @@
         <v>5.08900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.57669069641707</v>
+        <v>2.63877006808477</v>
       </c>
     </row>
     <row r="14">
@@ -3508,7 +1321,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.66777331342994</v>
+        <v>2.5148048536931</v>
       </c>
     </row>
     <row r="15">
@@ -3525,7 +1338,7 @@
         <v>1.311</v>
       </c>
       <c r="E15" t="n">
-        <v>1.21438716525998</v>
+        <v>1.20990439251918</v>
       </c>
     </row>
     <row r="16">
@@ -3542,7 +1355,7 @@
         <v>2.862</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.60786213599612</v>
+        <v>-0.381536576693416</v>
       </c>
     </row>
   </sheetData>
@@ -3584,10 +1397,10 @@
         <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.933333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3601,10 +1414,10 @@
         <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.933333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3618,10 +1431,10 @@
         <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>0.933333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3635,10 +1448,10 @@
         <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3652,10 +1465,10 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3669,10 +1482,10 @@
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -3686,10 +1499,10 @@
         <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3703,10 +1516,10 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -3720,10 +1533,10 @@
         <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -3737,10 +1550,10 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -3754,10 +1567,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -3771,10 +1584,10 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -3788,10 +1601,10 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.733333333333333</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3805,10 +1618,10 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="16">
@@ -3822,10 +1635,10 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17">
@@ -3839,10 +1652,10 @@
         <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18">
@@ -3856,10 +1669,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="19">
@@ -3873,10 +1686,10 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -3890,10 +1703,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="21">
@@ -3907,10 +1720,10 @@
         <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22">
@@ -3924,10 +1737,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="23">
@@ -3975,10 +1788,10 @@
         <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -3992,10 +1805,10 @@
         <v>62</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -4077,10 +1890,10 @@
         <v>67</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -4094,10 +1907,10 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="33">
@@ -4111,10 +1924,10 @@
         <v>69</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>0.533333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="34">
@@ -4196,10 +2009,10 @@
         <v>74</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="39">
@@ -4264,10 +2077,10 @@
         <v>78</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="43">
@@ -4298,10 +2111,10 @@
         <v>80</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="45">
@@ -4519,10 +2332,10 @@
         <v>93</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="58">
@@ -4536,10 +2349,10 @@
         <v>94</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="59">
@@ -4553,10 +2366,10 @@
         <v>95</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="60">
@@ -4570,10 +2383,10 @@
         <v>96</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="61">
@@ -4757,10 +2570,10 @@
         <v>107</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="72">
@@ -4774,10 +2587,10 @@
         <v>108</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="73">
@@ -4791,10 +2604,10 @@
         <v>109</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="74">
@@ -4808,10 +2621,10 @@
         <v>110</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="75">
@@ -4825,10 +2638,10 @@
         <v>111</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="76">
@@ -6222,6 +4035,125 @@
         <v>1</v>
       </c>
       <c r="E157" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="s">
+        <v>194</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="s">
+        <v>195</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="s">
+        <v>196</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="s">
+        <v>197</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="s">
+        <v>198</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="s">
+        <v>199</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="s">
+        <v>200</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T3/d_mcsa/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T3/d_mcsa/spls/c_data/results.xlsx
@@ -1040,7 +1040,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.408335001277076</v>
@@ -1048,10 +1048,18 @@
       <c r="I3" t="n">
         <v>0.271428571428571</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.348258706467662</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.174129353233831</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.68742690255068</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.628265213709135</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1075,6 +1083,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.736339686876147</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.0884493814905543</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.558999217753688</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.301958780047775</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.220905403316115</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.0238767240672997</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.961559394273742</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.172881655234992</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.594132693305064</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.52481124328543</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.35810242066833</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.0615720627812968</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.943394067649515</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.788440514015369</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.286113677120424</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.366112753774845</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.196326003783933</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.171730002852631</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.153527784197992</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.667492052860687</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.44508116736672</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.374542389421514</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.979342899422703</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.44843486146873</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-1.81654819626963</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0145933766127301</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.417568034028917</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.485032083790854</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-1.22672576005358</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.382038114882266</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.56128622244807</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.246415210888727</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.610380151278504</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.106666174369527</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.444209970995113</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-1.82622014535038</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.439038594559131</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.819835983382137</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-1.07340676773945</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.0681729413451067</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.896092504745945</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.0154224811917485</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-1.53630725318602</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.449085591125661</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0863019450808034</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.740153730655335</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.607805805858566</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-1.14088841528876</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.440540876383766</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.506732274067861</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.12213622027171</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.247318687232027</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.595182262082009</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.382751978210357</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.489425561798244</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.591623445475248</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.190351249570252</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.486712847594863</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.70087895905971</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.061536110047659</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1.18267214352501</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.789518847567856</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.06183516644953</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.35778361622647</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.813031762660916</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.433933388047848</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-2.71573186955472</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-1.18248821873333</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1.321550385753</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.318177010915948</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.430104983240063</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.185992153371206</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.185156791001873</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.367813143798998</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.846757189626481</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.095818348181734</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.429610065765711</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.42260772104657</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.507831534097726</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.239240024826345</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-1.11423832155087</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-2.37181957479279</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.288228391390285</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-1.11720453299106</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.443948712681741</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.083280459658994</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.103199154344391</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.970500582830829</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.174084316499483</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.543147500534947</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.699492322241585</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.387252240304022</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.128582610212569</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.897399864316765</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.544361076163258</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.162197760224958</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-1.22955681413302</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.217312167875867</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.751532036152806</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.89604257133965</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.27871168746664</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.506378943244777</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.08214292501354</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-1.85946092484588</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.624552261124188</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.512349286725355</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.570809799919256</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.821164405534333</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-1.30048739975613</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.282433226416335</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.779488078852904</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.433780002293392</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.0630194584473984</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.967182651246313</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.10054406603279</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.0688114039371488</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.736273714217939</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.828114647429566</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.402495399398974</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.444440020740587</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.872979584565547</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-1.03399946149949</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.940295990803923</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-1.09268239685571</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.763033661094898</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.561269447354674</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-1.66793478360563</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.730496291536888</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.576282280213262</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.91553894596416</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-2.43486995853512</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.413505661354606</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.341234877863151</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.19926812823546</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.460439103945128</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.831909833395572</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.187977359204068</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.265234589732514</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-1.00048900276072</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.24433251900451</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.788072377191655</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.253680757606129</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.992502780249179</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.670282781840982</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.953980337165389</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-1.07421985023853</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.833637892024055</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.808032525749153</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.227907390652099</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.48352820228276</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.914422221767228</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.216666587191215</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-1.27642407177108</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0.0816068651945625</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.586990925073066</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-1.37054727715581</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.032801504386782</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.277248851534871</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.508557041058815</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.213224706751636</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.0232718448083549</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.611403447681147</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.602960472653468</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-3.21163347158326</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.246860719473694</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.38237463526212</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-1.00258077232555</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1.96930762989574</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.78318992887488</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-1.67030692057972</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.751249395760368</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-1.54382137920405</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.650807554217732</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.282124348511718</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.154441365281903</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.326760898820886</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.836649402875778</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.39404203135796</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-1.17685052416537</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-1.45140328383071</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.285706160216272</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-2.71608786678314</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.214770772415922</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.774539928999618</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.30699264541026</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.378351031328572</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-2.08115304625758</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-1.2719683999863</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-1.09789596107299</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-1.20446054700882</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.954565410821714</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.222052947048381</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.18472443218861</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.0327967424006591</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.919462128492133</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.292360216375548</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.726093329503067</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.85489028709373</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-1.96561257804846</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.240165587127934</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
